--- a/data/trans_orig/Q5411-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2007</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35621</t>
+          <t>35280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73151</t>
+          <t>74741</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68160</t>
+          <t>68865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102149</t>
+          <t>104283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>337568</t>
+          <t>337909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355875</t>
+          <t>355799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>514598</t>
+          <t>513008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>544120</t>
+          <t>543098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>858789</t>
+          <t>856655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>892778</t>
+          <t>892073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>60153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136654</t>
+          <t>137698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148027</t>
+          <t>147420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>21276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59813</t>
+          <t>59327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>50278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82380</t>
+          <t>82118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75512</t>
+          <t>74520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113593</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>462405</t>
+          <t>463339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>482739</t>
+          <t>482626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>594462</t>
+          <t>594724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626164</t>
+          <t>626564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1065715</t>
+          <t>1067755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1103796</t>
+          <t>1104788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2012</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39508</t>
+          <t>41083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70199</t>
+          <t>72100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128285</t>
+          <t>127780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172056</t>
+          <t>171001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177649</t>
+          <t>177112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232947</t>
+          <t>231450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>344199</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>374890</t>
+          <t>373315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462489</t>
+          <t>463544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>506260</t>
+          <t>506765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>815995</t>
+          <t>817492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>871293</t>
+          <t>871830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106613</t>
+          <t>106152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116574</t>
+          <t>116592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68765</t>
+          <t>68564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79812</t>
+          <t>79895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179256</t>
+          <t>179066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194235</t>
+          <t>194233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46769</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80660</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138271</t>
+          <t>139738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>183634</t>
+          <t>183787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>196199</t>
+          <t>194497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252681</t>
+          <t>253783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478977</t>
+          <t>482159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512868</t>
+          <t>514686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>556231</t>
+          <t>556078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601594</t>
+          <t>600127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1046821</t>
+          <t>1045719</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1103303</t>
+          <t>1105005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2016</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>27610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>50206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68035</t>
+          <t>67257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106491</t>
+          <t>106832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104440</t>
+          <t>103562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148963</t>
+          <t>147772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302809</t>
+          <t>303695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325390</t>
+          <t>326291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448266</t>
+          <t>447925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>486722</t>
+          <t>487500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>759695</t>
+          <t>760886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>804218</t>
+          <t>805096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35112</t>
+          <t>35476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178379</t>
+          <t>177622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189062</t>
+          <t>188252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161277</t>
+          <t>162253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179730</t>
+          <t>180139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345494</t>
+          <t>345130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366776</t>
+          <t>367018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65936</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37398</t>
+          <t>36749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61005</t>
+          <t>61456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84530</t>
+          <t>83263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126487</t>
+          <t>127183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126719</t>
+          <t>127339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176229</t>
+          <t>174687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>527458</t>
+          <t>527007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551065</t>
+          <t>551714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650018</t>
+          <t>649322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691975</t>
+          <t>693242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1188739</t>
+          <t>1190281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238249</t>
+          <t>1237629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2023</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>43788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89025</t>
+          <t>89008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114634</t>
+          <t>116515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120453</t>
+          <t>121180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152558</t>
+          <t>153627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226152</t>
+          <t>225456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243479</t>
+          <t>243083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385147</t>
+          <t>383266</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>410756</t>
+          <t>410773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>616467</t>
+          <t>615398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>648572</t>
+          <t>647845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>252922</t>
+          <t>253627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>264818</t>
+          <t>264740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422561</t>
+          <t>423700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450662</t>
+          <t>450625</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>684489</t>
+          <t>683906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717041</t>
+          <t>716459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96634</t>
+          <t>97034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104236</t>
+          <t>104362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65885</t>
+          <t>66139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70949</t>
+          <t>70941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166868</t>
+          <t>167169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174587</t>
+          <t>174412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>39530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62473</t>
+          <t>61486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62301</t>
+          <t>63020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154946</t>
+          <t>156082</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105350</t>
+          <t>110125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200263</t>
+          <t>202878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>585014</t>
+          <t>586001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607557</t>
+          <t>607957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>871899</t>
+          <t>870763</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964544</t>
+          <t>963825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1474069</t>
+          <t>1471454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1568982</t>
+          <t>1564207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5411-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>44736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74741</t>
+          <t>75190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>67852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104283</t>
+          <t>103147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>337909</t>
+          <t>336999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355799</t>
+          <t>356092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>513008</t>
+          <t>512559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>543098</t>
+          <t>543013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>856655</t>
+          <t>857791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>892073</t>
+          <t>893086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51163</t>
+          <t>50887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137698</t>
+          <t>136538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147420</t>
+          <t>147355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21276</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59327</t>
+          <t>60548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111553</t>
+          <t>110795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>463339</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>482626</t>
+          <t>481695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>594724</t>
+          <t>594513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626564</t>
+          <t>627369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1067755</t>
+          <t>1068513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1104788</t>
+          <t>1105564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41083</t>
+          <t>41101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72100</t>
+          <t>69667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127780</t>
+          <t>127579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171001</t>
+          <t>170186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177112</t>
+          <t>178090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231450</t>
+          <t>232154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>344731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373315</t>
+          <t>373297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>463544</t>
+          <t>464359</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>506765</t>
+          <t>506966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>817492</t>
+          <t>816788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>871830</t>
+          <t>870852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106152</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116592</t>
+          <t>116538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68564</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79895</t>
+          <t>79896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179066</t>
+          <t>178453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194233</t>
+          <t>193852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47724</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139738</t>
+          <t>138292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>183787</t>
+          <t>185201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194497</t>
+          <t>192649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253783</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482159</t>
+          <t>480863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514686</t>
+          <t>513169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>556078</t>
+          <t>554664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>600127</t>
+          <t>601573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1045719</t>
+          <t>1050138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1105005</t>
+          <t>1106853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27610</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50206</t>
+          <t>50253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67257</t>
+          <t>69410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106832</t>
+          <t>105911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103562</t>
+          <t>103809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147772</t>
+          <t>146646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303695</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326291</t>
+          <t>326232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447925</t>
+          <t>448846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>487500</t>
+          <t>485347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>760886</t>
+          <t>762012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>805096</t>
+          <t>804849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25821</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35476</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177622</t>
+          <t>177817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188252</t>
+          <t>188259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162253</t>
+          <t>162064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180139</t>
+          <t>180208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345130</t>
+          <t>344827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>367018</t>
+          <t>365782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66518</t>
+          <t>65844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36749</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>61743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83263</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127183</t>
+          <t>126863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127339</t>
+          <t>124374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174687</t>
+          <t>174494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>527007</t>
+          <t>526720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551714</t>
+          <t>552966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>649322</t>
+          <t>649642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693242</t>
+          <t>692332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1190281</t>
+          <t>1190474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1237629</t>
+          <t>1240594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33643</t>
+          <t>35593</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43788</t>
+          <t>45388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>102081</t>
+          <t>109228</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89008</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116515</t>
+          <t>123009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>135724</t>
+          <t>144821</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121180</t>
+          <t>129365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153627</t>
+          <t>165499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>235601</t>
+          <t>254502</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225456</t>
+          <t>244707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243083</t>
+          <t>263191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>397700</t>
+          <t>428528</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383266</t>
+          <t>414747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>410773</t>
+          <t>441909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>633301</t>
+          <t>683030</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615398</t>
+          <t>662352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647845</t>
+          <t>698486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>499781</t>
+          <t>537756</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>499781</t>
+          <t>537756</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>499781</t>
+          <t>537756</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>769025</t>
+          <t>827851</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>769025</t>
+          <t>827851</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>769025</t>
+          <t>827851</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>32401</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>25108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45090</t>
+          <t>43063</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>259908</t>
+          <t>289856</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253627</t>
+          <t>282150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>264740</t>
+          <t>294823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>439796</t>
+          <t>259213</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423700</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450625</t>
+          <t>264333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>699704</t>
+          <t>549070</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683906</t>
+          <t>538408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>556363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>102326</t>
+          <t>115464</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97034</t>
+          <t>109389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104362</t>
+          <t>118165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69667</t>
+          <t>81330</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66139</t>
+          <t>77842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70941</t>
+          <t>82449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>171994</t>
+          <t>196794</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167169</t>
+          <t>190973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174412</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49651</t>
+          <t>52979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39530</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61486</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>119682</t>
+          <t>129186</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63020</t>
+          <t>115819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156082</t>
+          <t>146794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>169333</t>
+          <t>182165</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110125</t>
+          <t>164650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202878</t>
+          <t>202341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>597836</t>
+          <t>659822</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>586001</t>
+          <t>646313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607957</t>
+          <t>670340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>907163</t>
+          <t>769071</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>870763</t>
+          <t>751463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>963825</t>
+          <t>782438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1504999</t>
+          <t>1428894</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1471454</t>
+          <t>1408718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1564207</t>
+          <t>1446409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1026845</t>
+          <t>898257</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1026845</t>
+          <t>898257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1026845</t>
+          <t>898257</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1674332</t>
+          <t>1611059</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1674332</t>
+          <t>1611059</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1674332</t>
+          <t>1611059</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
